--- a/dist/print/05-tracker-workbook.xlsx
+++ b/dist/print/05-tracker-workbook.xlsx
@@ -43,7 +43,7 @@
     <t xml:space="preserve">This workbook has no macros. Every computed column uses ordinary spreadsheet formulas, so it keeps working if you copy or import it into another spreadsheet application.</t>
   </si>
   <si>
-    <t xml:space="preserve">Not endorsed by or affiliated with Riot Games. League of Legends is a trademark of Riot Games, Inc.</t>
+    <t xml:space="preserve">Solo Queue Practice System was created under Riot Games’ “Legal Jibber Jabber” policy using assets owned by Riot Games. Riot Games does not endorse or sponsor this project. League of Legends is a trademark of Riot Games, Inc.</t>
   </si>
   <si>
     <t xml:space="preserve">v1.0.0 - last reviewed 2026-08-12</t>
@@ -235,7 +235,7 @@
     <t xml:space="preserve">Stretch target:</t>
   </si>
   <si>
-    <t xml:space="preserve">The stricter practice-tool challenge target -- roughly perfect last-hitting with minimal jungle-camp cheats.</t>
+    <t xml:space="preserve">The stricter practice-tool challenge target — roughly perfect last-hitting with minimal jungle-camp cheats.</t>
   </si>
 </sst>
 </file>

--- a/dist/print/05-tracker-workbook.xlsx
+++ b/dist/print/05-tracker-workbook.xlsx
@@ -235,7 +235,7 @@
     <t xml:space="preserve">Stretch target:</t>
   </si>
   <si>
-    <t xml:space="preserve">The stricter practice-tool challenge target — roughly perfect last-hitting with minimal jungle-camp cheats.</t>
+    <t xml:space="preserve">The stricter practice-tool challenge target - roughly perfect last-hitting with minimal jungle-camp cheats.</t>
   </si>
 </sst>
 </file>
